--- a/advantest/dist/20261025_Advantest模型_v0.3.1.xlsx
+++ b/advantest/dist/20261025_Advantest模型_v0.3.1.xlsx
@@ -5548,26 +5548,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5841,26 +5841,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6138,26 +6138,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6289,26 +6289,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6460,26 +6460,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6611,26 +6611,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6773,26 +6773,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7000,26 +7000,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7212,26 +7212,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7363,26 +7363,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7620,26 +7620,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7771,26 +7771,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7933,26 +7933,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8084,26 +8084,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8324,26 +8324,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8692,26 +8692,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8816,26 +8816,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9015,26 +9015,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9136,26 +9136,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9257,26 +9257,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9378,26 +9378,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9499,26 +9499,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
